--- a/港岛-半山区西部-罗便臣道80号/罗便臣道80号_销控明细表.xlsx
+++ b/港岛-半山区西部-罗便臣道80号/罗便臣道80号_销控明细表.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -125,6 +125,11 @@
       <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -202,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -268,6 +273,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -764,7 +772,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2016-09-15</t>
+          <t>2016-09-16</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -900,7 +908,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2017-01-12</t>
+          <t>2017-01-13</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -966,7 +974,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2016-09-01</t>
+          <t>2016-09-02</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1032,7 +1040,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1098,7 +1106,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1164,7 +1172,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1230,7 +1238,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1296,7 +1304,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1362,7 +1370,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1428,7 +1436,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1494,7 +1502,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1560,7 +1568,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1691,23 +1699,19 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>36800000</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>33980</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1836,7 +1840,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2015-11-24</t>
+          <t>2015-11-25</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1902,7 +1906,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2015-10-18</t>
+          <t>2015-10-19</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1968,7 +1972,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2011-02-20</t>
+          <t>2011-02-21</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -2034,7 +2038,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2016-07-11</t>
+          <t>2016-07-12</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2100,7 +2104,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2166,7 +2170,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2232,7 +2236,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2298,7 +2302,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2364,7 +2368,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2430,7 +2434,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2496,7 +2500,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2632,7 +2636,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2698,7 +2702,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2764,7 +2768,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2830,7 +2834,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2896,7 +2900,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2016-10-31</t>
+          <t>2016-11-01</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2962,7 +2966,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2016-06-13</t>
+          <t>2016-06-14</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -3028,7 +3032,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2011-01-09</t>
+          <t>2011-01-10</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -3094,7 +3098,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2016-10-06</t>
+          <t>2016-10-07</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3160,7 +3164,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3296,7 +3300,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3362,7 +3366,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3428,7 +3432,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3494,7 +3498,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3560,7 +3564,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3626,7 +3630,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3692,7 +3696,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3758,7 +3762,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3824,7 +3828,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3890,7 +3894,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3956,7 +3960,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -4022,7 +4026,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -4088,7 +4092,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -4154,7 +4158,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4360,7 +4364,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2002-01-08</t>
+          <t>2002-01-09</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4566,7 +4570,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4632,7 +4636,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2002-01-02</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4698,7 +4702,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4764,7 +4768,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2001-12-28</t>
+          <t>2001-12-29</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4900,7 +4904,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2001-12-28</t>
+          <t>2001-12-29</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -5106,7 +5110,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -5172,7 +5176,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -5308,7 +5312,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2016-06-07</t>
+          <t>2016-06-08</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5374,7 +5378,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2015-10-04</t>
+          <t>2015-10-05</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5440,7 +5444,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2011-01-11</t>
+          <t>2011-01-12</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5506,7 +5510,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2011-01-18</t>
+          <t>2011-01-19</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5572,7 +5576,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5638,7 +5642,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5704,7 +5708,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5770,7 +5774,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5836,7 +5840,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2002-01-10</t>
+          <t>2002-01-11</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5902,7 +5906,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5968,7 +5972,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -6104,7 +6108,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -6170,7 +6174,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -6236,7 +6240,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -6302,7 +6306,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -6368,7 +6372,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6434,7 +6438,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6500,7 +6504,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6566,7 +6570,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6632,7 +6636,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6698,7 +6702,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6764,7 +6768,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6830,7 +6834,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6896,7 +6900,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2002-02-15</t>
+          <t>2002-02-16</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -7102,7 +7106,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -7168,7 +7172,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2001-12-28</t>
+          <t>2001-12-29</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -7234,7 +7238,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -7300,7 +7304,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -7366,7 +7370,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2001-12-28</t>
+          <t>2001-12-29</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -7432,7 +7436,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7498,7 +7502,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7564,7 +7568,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7700,7 +7704,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2002-01-07</t>
+          <t>2002-01-08</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7766,7 +7770,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2011-06-16</t>
+          <t>2011-06-17</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7832,7 +7836,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2011-01-17</t>
+          <t>2011-01-18</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7898,7 +7902,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2002-01-02</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7964,7 +7968,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2011-01-23</t>
+          <t>2011-01-24</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -8030,7 +8034,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2015-09-28</t>
+          <t>2015-09-29</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -8096,7 +8100,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2002-03-25</t>
+          <t>2002-03-26</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -8162,7 +8166,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2001-12-30</t>
+          <t>2001-12-31</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -8228,7 +8232,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2001-12-28</t>
+          <t>2001-12-29</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -8294,7 +8298,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2001-12-28</t>
+          <t>2001-12-29</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -8360,7 +8364,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2011-01-20</t>
+          <t>2011-01-21</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -8426,7 +8430,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2001-12-27</t>
+          <t>2001-12-28</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -8492,7 +8496,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2002-02-18</t>
+          <t>2002-02-19</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8558,7 +8562,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2016-10-13</t>
+          <t>2016-10-14</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8624,7 +8628,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2011-02-28</t>
+          <t>2011-03-01</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8690,7 +8694,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2002-01-08</t>
+          <t>2002-01-09</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8756,7 +8760,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2002-01-02</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8822,7 +8826,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2016-06-13</t>
+          <t>2016-06-14</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8888,7 +8892,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2011-03-21</t>
+          <t>2011-03-22</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8954,7 +8958,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2002-01-02</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -9020,7 +9024,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2001-12-30</t>
+          <t>2001-12-31</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -9086,7 +9090,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2015-12-23</t>
+          <t>2015-12-24</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -9152,7 +9156,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2004-11-12</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -9218,7 +9222,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2002-01-07</t>
+          <t>2002-01-08</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -9284,7 +9288,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2015-11-17</t>
+          <t>2015-11-18</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -9350,7 +9354,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2015-11-19</t>
+          <t>2015-11-20</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -9416,7 +9420,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2007-08-23</t>
+          <t>2007-08-24</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -9482,7 +9486,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2006-08-16</t>
+          <t>2006-08-17</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -9548,7 +9552,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2007-06-28</t>
+          <t>2007-06-29</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9684,7 +9688,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2015-09-10</t>
+          <t>2015-09-11</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -9750,7 +9754,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2007-08-22</t>
+          <t>2007-08-23</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9886,7 +9890,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2016-07-13</t>
+          <t>2016-07-14</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9952,7 +9956,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2011-05-18</t>
+          <t>2011-05-19</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -10018,7 +10022,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2015-12-27</t>
+          <t>2015-12-28</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -10084,7 +10088,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2016-01-06</t>
+          <t>2016-01-07</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -10150,7 +10154,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2011-03-20</t>
+          <t>2011-03-21</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -10286,7 +10290,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -10352,7 +10356,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -10698,7 +10702,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2002-01-02</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10764,7 +10768,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2017-07-31</t>
+          <t>2017-08-01</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10830,7 +10834,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2011-06-27</t>
+          <t>2011-06-28</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10896,7 +10900,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2011-06-27</t>
+          <t>2011-06-28</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -10962,7 +10966,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2017-07-30</t>
+          <t>2017-07-31</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -11028,7 +11032,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -11094,7 +11098,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -11160,7 +11164,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2011-04-12</t>
+          <t>2011-04-13</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -11226,7 +11230,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2011-06-14</t>
+          <t>2011-06-15</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -11292,7 +11296,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2015-11-11</t>
+          <t>2015-11-12</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -11358,7 +11362,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2015-12-01</t>
+          <t>2015-12-02</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -11424,7 +11428,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2011-01-18</t>
+          <t>2011-01-19</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -11490,7 +11494,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2010-12-30</t>
+          <t>2010-12-31</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -11556,7 +11560,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2015-11-08</t>
+          <t>2015-11-09</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -11622,7 +11626,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2015-12-23</t>
+          <t>2015-12-24</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -11688,7 +11692,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2011-01-12</t>
+          <t>2011-01-13</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -11754,7 +11758,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2002-01-02</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11820,7 +11824,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2011-01-23</t>
+          <t>2011-01-24</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -11886,7 +11890,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2015-09-29</t>
+          <t>2015-09-30</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -11952,7 +11956,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2016-06-21</t>
+          <t>2016-06-22</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -12018,7 +12022,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2011-01-23</t>
+          <t>2011-01-24</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -12084,7 +12088,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2002-01-08</t>
+          <t>2002-01-09</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -12360,7 +12364,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -12426,7 +12430,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2008-03-26</t>
+          <t>2008-03-27</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -12492,7 +12496,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2011-05-29</t>
+          <t>2011-05-30</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -12558,7 +12562,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2016-06-13</t>
+          <t>2016-06-14</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -12624,7 +12628,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2011-06-01</t>
+          <t>2011-06-02</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -12690,7 +12694,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2011-01-26</t>
+          <t>2011-01-27</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -12756,7 +12760,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2011-01-16</t>
+          <t>2011-01-17</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -12822,7 +12826,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2002-01-02</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12888,7 +12892,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2002-04-19</t>
+          <t>2002-04-20</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -13024,7 +13028,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2011-01-16</t>
+          <t>2011-01-17</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -13090,7 +13094,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2011-01-23</t>
+          <t>2011-01-24</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -13156,7 +13160,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2011-06-13</t>
+          <t>2011-06-14</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -13222,7 +13226,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2011-03-08</t>
+          <t>2011-03-09</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -13288,7 +13292,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2011-01-18</t>
+          <t>2011-01-19</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -13354,7 +13358,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2002-01-08</t>
+          <t>2002-01-09</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -13420,7 +13424,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2015-11-05</t>
+          <t>2015-11-06</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -13486,7 +13490,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2011-01-18</t>
+          <t>2011-01-19</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -13552,7 +13556,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2011-01-06</t>
+          <t>2011-01-07</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -13618,7 +13622,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2002-01-16</t>
+          <t>2002-01-17</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -13684,7 +13688,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2011-03-16</t>
+          <t>2011-03-17</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -13750,7 +13754,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2011-01-23</t>
+          <t>2011-01-24</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -13811,7 +13815,7 @@
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G199" s="3" t="inlineStr">
@@ -13821,12 +13825,12 @@
       </c>
       <c r="H199" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I199" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J199" s="3" t="inlineStr">
@@ -13836,12 +13840,12 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L199" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M199" s="3" t="inlineStr">
@@ -13851,7 +13855,7 @@
       </c>
       <c r="N199" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -13886,7 +13890,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2002-01-02</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -13952,7 +13956,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2002-01-02</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -14018,7 +14022,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2011-01-13</t>
+          <t>2011-01-14</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -14084,7 +14088,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2011-01-17</t>
+          <t>2011-01-18</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -14150,7 +14154,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2002-01-02</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -14216,7 +14220,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2015-11-12</t>
+          <t>2015-11-13</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -14282,7 +14286,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2011-01-30</t>
+          <t>2011-01-31</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -14348,7 +14352,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2011-01-16</t>
+          <t>2011-01-17</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -14414,7 +14418,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2002-01-08</t>
+          <t>2002-01-09</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -14480,7 +14484,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2002-01-09</t>
+          <t>2002-01-10</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -14616,7 +14620,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2002-01-02</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -14682,7 +14686,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2002-01-02</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -14748,7 +14752,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2002-01-02</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -14884,7 +14888,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2010-12-30</t>
+          <t>2010-12-31</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -14950,7 +14954,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2002-01-02</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -15016,7 +15020,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2011-01-31</t>
+          <t>2011-02-01</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -15082,7 +15086,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2011-01-10</t>
+          <t>2011-01-11</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -15148,7 +15152,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2011-01-13</t>
+          <t>2011-01-14</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -15214,7 +15218,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2001-12-28</t>
+          <t>2001-12-29</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -15280,7 +15284,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2011-01-23</t>
+          <t>2011-01-24</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -15346,7 +15350,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2011-01-11</t>
+          <t>2011-01-12</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -15412,7 +15416,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2010-12-28</t>
+          <t>2010-12-29</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -15478,7 +15482,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2002-01-08</t>
+          <t>2002-01-09</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -15544,7 +15548,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2002-01-02</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -15610,7 +15614,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2010-12-19</t>
+          <t>2010-12-20</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -15676,7 +15680,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2010-12-19</t>
+          <t>2010-12-20</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -15742,7 +15746,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2002-01-02</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -15808,7 +15812,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2002-01-07</t>
+          <t>2002-01-08</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -15874,7 +15878,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2002-01-02</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -15940,7 +15944,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2011-01-05</t>
+          <t>2011-01-06</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -16006,7 +16010,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2002-01-02</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -16142,7 +16146,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2011-01-20</t>
+          <t>2011-01-21</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -16208,7 +16212,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2002-01-09</t>
+          <t>2002-01-10</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -16274,7 +16278,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2002-03-15</t>
+          <t>2002-03-16</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -16340,7 +16344,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2002-01-08</t>
+          <t>2002-01-09</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -16406,7 +16410,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2002-01-08</t>
+          <t>2002-01-09</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -16472,7 +16476,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2001-12-28</t>
+          <t>2001-12-29</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -16538,7 +16542,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2002-01-08</t>
+          <t>2002-01-09</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -16604,7 +16608,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2002-01-09</t>
+          <t>2002-01-10</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -16670,7 +16674,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2002-01-02</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -16736,7 +16740,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2002-01-02</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -16802,7 +16806,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2002-01-02</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -16868,7 +16872,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2002-01-02</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -16934,7 +16938,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2002-01-07</t>
+          <t>2002-01-08</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -17000,7 +17004,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2002-01-02</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -17066,7 +17070,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2002-01-02</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -17132,7 +17136,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2002-01-09</t>
+          <t>2002-01-10</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -17198,7 +17202,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2001-12-27</t>
+          <t>2001-12-28</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -17264,7 +17268,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2001-12-27</t>
+          <t>2001-12-28</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -17330,7 +17334,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2001-12-27</t>
+          <t>2001-12-28</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -17396,7 +17400,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2011-01-16</t>
+          <t>2011-01-17</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -17462,7 +17466,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2002-01-08</t>
+          <t>2002-01-09</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -17528,7 +17532,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2002-01-08</t>
+          <t>2002-01-09</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -17594,7 +17598,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2002-01-08</t>
+          <t>2002-01-09</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -17660,7 +17664,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2002-01-02</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -17726,7 +17730,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2002-01-02</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -17792,7 +17796,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2002-01-02</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -17858,7 +17862,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2002-01-02</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -17924,7 +17928,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2001-12-28</t>
+          <t>2001-12-29</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -17990,7 +17994,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2001-12-28</t>
+          <t>2001-12-29</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -18056,7 +18060,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2001-12-30</t>
+          <t>2001-12-31</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -18122,7 +18126,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2002-01-09</t>
+          <t>2002-01-10</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -18188,7 +18192,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2002-01-09</t>
+          <t>2002-01-10</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -18254,7 +18258,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2001-12-28</t>
+          <t>2001-12-29</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -18371,7 +18375,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>113</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -18381,7 +18385,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -18423,7 +18427,7 @@
           <t>A | 2059呎 (3房)
 $8888万
 $43,167/呎
-(16年-09月-01日)</t>
+(16年-09月-02日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -18431,7 +18435,7 @@
           <t>B | 2093呎 (3房)
 $10528万
 $50,301/呎
-(17年-01月-12日)</t>
+(17年-01月-13日)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
@@ -18447,7 +18451,7 @@
           <t>D | 1709呎 (3房)
 $6300万
 $36,864/呎
-(16年-09月-15日)</t>
+(16年-09月-16日)</t>
         </is>
       </c>
     </row>
@@ -18462,7 +18466,7 @@
           <t>A | 1058呎 (3房)
 $52262万
 $493,971/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -18470,7 +18474,7 @@
           <t>B | 1070呎 (3房)
 $52262万
 $488,431/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -18478,7 +18482,7 @@
           <t>C | 855呎 (3房)
 $52262万
 $611,253/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -18486,7 +18490,7 @@
           <t>D | 855呎 (3房)
 $52262万
 $611,253/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
     </row>
@@ -18501,7 +18505,7 @@
           <t>A | 1052呎 (3房)
 $52262万
 $496,788/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -18509,7 +18513,7 @@
           <t>B | 1083呎 (3房)
 $52262万
 $482,568/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -18517,7 +18521,7 @@
           <t>C | 879呎 (3房)
 $52262万
 $594,563/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -18525,7 +18529,7 @@
           <t>D | 855呎 (3房)
 $52262万
 $611,253/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
     </row>
@@ -18543,12 +18547,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 1083呎 (3房)
--
--
-(待售)</t>
+$3680万
+$33,980/呎
+(26年-07月-24日)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -18564,7 +18568,7 @@
           <t>D | 855呎 (3房)
 $2550万
 $29,825/呎
-(26年-02月-19日)</t>
+(26年-02月-20日)</t>
         </is>
       </c>
     </row>
@@ -18579,7 +18583,7 @@
           <t>A | 1052呎 (3房)
 $3467万
 $32,956/呎
-(16年-07月-11日)</t>
+(16年-07月-12日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -18587,7 +18591,7 @@
           <t>B | 1070呎 (3房)
 $3130万
 $29,252/呎
-(11年-02月-20日)</t>
+(11年-02月-21日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -18595,7 +18599,7 @@
           <t>C | 855呎 (3房)
 $2866万
 $33,518/呎
-(15年-10月-18日)</t>
+(15年-10月-19日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -18603,7 +18607,7 @@
           <t>D | 855呎 (3房)
 $2643万
 $30,917/呎
-(15年-11月-24日)</t>
+(15年-11月-25日)</t>
         </is>
       </c>
     </row>
@@ -18618,7 +18622,7 @@
           <t>A | 1052呎 (3房)
 $52262万
 $496,788/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -18626,7 +18630,7 @@
           <t>B | 1070呎 (3房)
 $52262万
 $488,431/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -18634,7 +18638,7 @@
           <t>C | 855呎 (3房)
 $52262万
 $611,253/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -18642,7 +18646,7 @@
           <t>D | 855呎 (3房)
 $52262万
 $611,253/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
     </row>
@@ -18665,7 +18669,7 @@
           <t>B | 1070呎 (3房)
 $3250万
 $30,374/呎
-(26年-03月-04日)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -18673,7 +18677,7 @@
           <t>C | 855呎 (3房)
 $2830万
 $33,099/呎
-(26年-04月-28日)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -18681,7 +18685,7 @@
           <t>D | 855呎 (3房)
 $2620万
 $30,643/呎
-(26年-05月-03日)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
     </row>
@@ -18696,7 +18700,7 @@
           <t>A | 1052呎 (3房)
 $52262万
 $496,788/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -18704,7 +18708,7 @@
           <t>B | 1070呎 (3房)
 $52262万
 $488,431/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -18712,7 +18716,7 @@
           <t>C | 855呎 (3房)
 $52262万
 $611,253/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -18720,7 +18724,7 @@
           <t>D | 879呎 (3房)
 $52262万
 $594,563/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
     </row>
@@ -18735,7 +18739,7 @@
           <t>A | 1052呎 (3房)
 $3426万
 $32,564/呎
-(16年-10月-06日)</t>
+(16年-10月-07日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -18743,7 +18747,7 @@
           <t>B | 1083呎 (3房)
 $2950万
 $27,239/呎
-(11年-01月-09日)</t>
+(11年-01月-10日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -18751,7 +18755,7 @@
           <t>C | 855呎 (3房)
 $2833万
 $33,133/呎
-(16年-06月-13日)</t>
+(16年-06月-14日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -18759,7 +18763,7 @@
           <t>D | 855呎 (3房)
 $2640万
 $30,871/呎
-(16年-10月-31日)</t>
+(16年-11月-01日)</t>
         </is>
       </c>
     </row>
@@ -18774,7 +18778,7 @@
           <t>A | 1052呎 (3房)
 $3100万
 $29,468/呎
-(26年-04月-28日)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -18782,7 +18786,7 @@
           <t>B | 1070呎 (3房)
 $3418万
 $31,944/呎
-(26年-04月-07日)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -18798,7 +18802,7 @@
           <t>D | 855呎 (3房)
 $2430万
 $28,421/呎
-(26年-02月-10日)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
     </row>
@@ -18813,7 +18817,7 @@
           <t>A | 1032呎 (3房)
 $52262万
 $506,416/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -18821,7 +18825,7 @@
           <t>B | 1064呎 (3房)
 $52262万
 $491,185/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -18829,7 +18833,7 @@
           <t>C | 841呎 (3房)
 $52262万
 $621,428/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -18837,7 +18841,7 @@
           <t>D | 841呎 (3房)
 $52262万
 $621,428/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
     </row>
@@ -18852,7 +18856,7 @@
           <t>A | 1032呎 (3房)
 $52262万
 $506,416/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -18860,7 +18864,7 @@
           <t>B | 1052呎 (3房)
 $52262万
 $496,788/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -18868,7 +18872,7 @@
           <t>C | 841呎 (3房)
 $52262万
 $621,428/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -18876,7 +18880,7 @@
           <t>D | 841呎 (3房)
 $52262万
 $621,428/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
     </row>
@@ -18891,7 +18895,7 @@
           <t>A | 1032呎 (3房)
 $52262万
 $506,416/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -18899,7 +18903,7 @@
           <t>B | 1052呎 (3房)
 $52262万
 $496,788/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -18907,7 +18911,7 @@
           <t>C | 865呎 (3房)
 $52262万
 $604,186/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -18915,7 +18919,7 @@
           <t>D | 841呎 (3房)
 $52262万
 $621,428/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
     </row>
@@ -18938,7 +18942,7 @@
           <t>B | 1052呎 (3房)
 $1269万
 $12,064/呎
-(02年-01月-08日)</t>
+(02年-01月-09日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -18969,7 +18973,7 @@
           <t>A | 1032呎 (3房)
 $3030万
 $29,360/呎
-(26年-06月-15日)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -18977,7 +18981,7 @@
           <t>B | 1052呎 (3房)
 $1255万
 $11,931/呎
-(02年-01月-01日)</t>
+(02年-01月-02日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -18985,7 +18989,7 @@
           <t>C | 841呎 (3房)
 $2550万
 $30,321/呎
-(26年-04月-13日)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -19016,7 +19020,7 @@
           <t>B | 1052呎 (3房)
 $1305万
 $12,405/呎
-(01年-12月-28日)</t>
+(01年-12月-29日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -19032,7 +19036,7 @@
           <t>D | 840呎 (2房)
 $1008万
 $11,994/呎
-(01年-12月-28日)</t>
+(01年-12月-29日)</t>
         </is>
       </c>
     </row>
@@ -19055,7 +19059,7 @@
           <t>B | 1052呎 (3房)
 $2750万
 $26,141/呎
-(26年-02月-09日)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -19063,7 +19067,7 @@
           <t>C | 865呎 (3房)
 $2370万
 $27,399/呎
-(26年-03月-03日)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -19086,7 +19090,7 @@
           <t>A | 1032呎 (3房)
 $2280万
 $22,093/呎
-(11年-01月-18日)</t>
+(11年-01月-19日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -19094,7 +19098,7 @@
           <t>B | 1065呎 (3房)
 $2553万
 $23,972/呎
-(11年-01月-11日)</t>
+(11年-01月-12日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -19102,7 +19106,7 @@
           <t>C | 841呎 (3房)
 $2578万
 $30,649/呎
-(15年-10月-04日)</t>
+(15年-10月-05日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -19110,7 +19114,7 @@
           <t>D | 840呎 (2房)
 $2339万
 $27,842/呎
-(16年-06月-07日)</t>
+(16年-06月-08日)</t>
         </is>
       </c>
     </row>
@@ -19125,7 +19129,7 @@
           <t>A | 1032呎 (3房)
 $52262万
 $506,416/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -19133,7 +19137,7 @@
           <t>B | 1052呎 (3房)
 $52262万
 $496,788/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -19141,7 +19145,7 @@
           <t>C | 841呎 (3房)
 $52262万
 $621,428/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -19149,7 +19153,7 @@
           <t>D | 840呎 (2房)
 $52262万
 $622,168/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
     </row>
@@ -19172,7 +19176,7 @@
           <t>B | 1052呎 (3房)
 $2800万
 $26,616/呎
-(26年-03月-12日)</t>
+(26年-03月-13日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -19180,7 +19184,7 @@
           <t>C | 841呎 (3房)
 $2350万
 $27,943/呎
-(26年-03月-10日)</t>
+(26年-03月-11日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -19188,7 +19192,7 @@
           <t>D | 840呎 (2房)
 $889万
 $10,585/呎
-(02年-01月-10日)</t>
+(02年-01月-11日)</t>
         </is>
       </c>
     </row>
@@ -19203,7 +19207,7 @@
           <t>A | 1032呎 (3房)
 $52262万
 $506,416/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -19211,7 +19215,7 @@
           <t>B | 1052呎 (3房)
 $52262万
 $496,788/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -19219,7 +19223,7 @@
           <t>C | 841呎 (3房)
 $52262万
 $621,428/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -19227,7 +19231,7 @@
           <t>D | 840呎 (2房)
 $52262万
 $622,168/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
     </row>
@@ -19242,7 +19246,7 @@
           <t>A | 1032呎 (3房)
 $52262万
 $506,416/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -19250,7 +19254,7 @@
           <t>B | 1064呎 (3房)
 $52262万
 $491,185/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -19258,7 +19262,7 @@
           <t>C | 865呎 (3房)
 $52262万
 $604,186/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -19266,7 +19270,7 @@
           <t>D | 840呎 (2房)
 $52262万
 $622,168/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
     </row>
@@ -19281,7 +19285,7 @@
           <t>A | 1032呎 (3房)
 $52262万
 $506,416/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -19289,7 +19293,7 @@
           <t>B | 1052呎 (3房)
 $52262万
 $496,788/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -19297,7 +19301,7 @@
           <t>C | 841呎 (3房)
 $52262万
 $621,428/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -19305,7 +19309,7 @@
           <t>D | 840呎 (2房)
 $52262万
 $622,168/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
     </row>
@@ -19320,7 +19324,7 @@
           <t>A | 1032呎 (3房)
 $52262万
 $506,416/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
@@ -19344,7 +19348,7 @@
           <t>D | 840呎 (2房)
 $894万
 $10,637/呎
-(02年-02月-15日)</t>
+(02年-02月-16日)</t>
         </is>
       </c>
     </row>
@@ -19359,7 +19363,7 @@
           <t>A | 1032呎 (3房)
 $998万
 $9,671/呎
-(01年-12月-28日)</t>
+(01年-12月-29日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -19367,7 +19371,7 @@
           <t>B | 1042呎 (3房)
 $2680万
 $25,720/呎
-(26年-03月-02日)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -19375,7 +19379,7 @@
           <t>C | 841呎 (3房)
 $2370万
 $28,181/呎
-(26年-07月-09日)</t>
+(26年-07月-10日)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
@@ -19383,7 +19387,7 @@
           <t>D | 840呎 (2房)
 $843万
 $10,032/呎
-(01年-12月-28日)</t>
+(01年-12月-29日)</t>
         </is>
       </c>
     </row>
@@ -19406,7 +19410,7 @@
           <t>B | 1056呎 (3房)
 $52262万
 $494,906/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -19414,7 +19418,7 @@
           <t>C | 841呎 (3房)
 $52262万
 $621,428/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr">
@@ -19422,7 +19426,7 @@
           <t>D | 840呎 (2房)
 $52262万
 $622,168/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
     </row>
@@ -19437,7 +19441,7 @@
           <t>A | 620呎 (2房)
 $550万
 $8,863/呎
-(02年-01月-01日)</t>
+(02年-01月-02日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -19445,7 +19449,7 @@
           <t>B | 1042呎 (3房)
 $2088万
 $20,038/呎
-(11年-01月-17日)</t>
+(11年-01月-18日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -19453,7 +19457,7 @@
           <t>C | 841呎 (3房)
 $1960万
 $23,306/呎
-(11年-06月-16日)</t>
+(11年-06月-17日)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -19461,7 +19465,7 @@
           <t>D | 840呎 (2房)
 $760万
 $9,048/呎
-(02年-01月-07日)</t>
+(02年-01月-08日)</t>
         </is>
       </c>
     </row>
@@ -19476,7 +19480,7 @@
           <t>A | 618呎 (2房)
 $465万
 $7,518/呎
-(01年-12月-30日)</t>
+(01年-12月-31日)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -19484,7 +19488,7 @@
           <t>B | 1042呎 (3房)
 $1049万
 $10,067/呎
-(02年-03月-25日)</t>
+(02年-03月-26日)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -19492,7 +19496,7 @@
           <t>C | 841呎 (3房)
 $2083万
 $24,774/呎
-(15年-09月-28日)</t>
+(15年-09月-29日)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -19500,7 +19504,7 @@
           <t>D | 840呎 (2房)
 $1670万
 $19,881/呎
-(11年-01月-23日)</t>
+(11年-01月-24日)</t>
         </is>
       </c>
     </row>
@@ -19515,7 +19519,7 @@
           <t>A | 618呎 (2房)
 $482万
 $7,799/呎
-(01年-12月-27日)</t>
+(01年-12月-28日)</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
@@ -19523,7 +19527,7 @@
           <t>B | 1042呎 (3房)
 $2188万
 $20,998/呎
-(11年-01月-20日)</t>
+(11年-01月-21日)</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -19531,7 +19535,7 @@
           <t>C | 841呎 (3房)
 $881万
 $10,476/呎
-(01年-12月-28日)</t>
+(01年-12月-29日)</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
@@ -19539,7 +19543,7 @@
           <t>D | 840呎 (2房)
 $785万
 $9,345/呎
-(01年-12月-28日)</t>
+(01年-12月-29日)</t>
         </is>
       </c>
     </row>
@@ -19554,7 +19558,7 @@
           <t>A | 618呎 (2房)
 $529万
 $8,560/呎
-(02年-01月-08日)</t>
+(02年-01月-09日)</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
@@ -19562,7 +19566,7 @@
           <t>B | 1042呎 (3房)
 $2210万
 $21,209/呎
-(11年-02月-28日)</t>
+(11年-03月-01日)</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
@@ -19570,7 +19574,7 @@
           <t>C | 841呎 (3房)
 $2034万
 $24,186/呎
-(16年-10月-13日)</t>
+(16年-10月-14日)</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr">
@@ -19578,7 +19582,7 @@
           <t>D | 840呎 (2房)
 $690万
 $8,211/呎
-(02年-02月-18日)</t>
+(02年-02月-19日)</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19597,7 @@
           <t>A | 618呎 (2房)
 $520万
 $8,414/呎
-(02年-01月-01日)</t>
+(02年-01月-02日)</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
@@ -19601,7 +19605,7 @@
           <t>B | 1056呎 (3房)
 $2158万
 $20,438/呎
-(11年-03月-21日)</t>
+(11年-03月-22日)</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
@@ -19609,7 +19613,7 @@
           <t>C | 841呎 (3房)
 $2040万
 $24,257/呎
-(16年-06月-13日)</t>
+(16年-06月-14日)</t>
         </is>
       </c>
       <c r="E35" s="20" t="inlineStr">
@@ -19617,7 +19621,7 @@
           <t>D | 840呎 (2房)
 $730万
 $8,692/呎
-(02年-01月-01日)</t>
+(02年-01月-02日)</t>
         </is>
       </c>
     </row>
@@ -19632,7 +19636,7 @@
           <t>A | 618呎 (2房)
 $433万
 $7,010/呎
-(02年-01月-07日)</t>
+(02年-01月-08日)</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
@@ -19640,7 +19644,7 @@
           <t>B | 1042呎 (3房)
 $52262万
 $501,556/呎
-(04年-11月-11日)</t>
+(04年-11月-12日)</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
@@ -19648,7 +19652,7 @@
           <t>C | 841呎 (3房)
 $4719万
 $56,108/呎
-(15年-12月-23日)</t>
+(15年-12月-24日)</t>
         </is>
       </c>
       <c r="E36" s="20" t="inlineStr">
@@ -19656,7 +19660,7 @@
           <t>D | 840呎 (2房)
 $662万
 $7,883/呎
-(01年-12月-30日)</t>
+(01年-12月-31日)</t>
         </is>
       </c>
     </row>
@@ -19672,7 +19676,7 @@
           <t>B | 1042呎 (3房)
 $2561万
 $24,579/呎
-(15年-11月-19日)</t>
+(15年-11月-20日)</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
@@ -19680,7 +19684,7 @@
           <t>C | 841呎 (3房)
 $1911万
 $22,717/呎
-(15年-11月-17日)</t>
+(15年-11月-18日)</t>
         </is>
       </c>
       <c r="E37" s="22" t="inlineStr"/>
@@ -19762,22 +19766,22 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -19827,7 +19831,7 @@
           <t>B | 1995呎 (3房)
 $4300万
 $21,554/呎
-(07年-06月-28日)</t>
+(07年-06月-29日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -19835,7 +19839,7 @@
           <t>C | 1366呎 (3房)
 $2963万
 $21,690/呎
-(06年-08月-16日)</t>
+(06年-08月-17日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -19843,7 +19847,7 @@
           <t>D | 1366呎 (3房)
 $3330万
 $24,378/呎
-(07年-08月-23日)</t>
+(07年-08月-24日)</t>
         </is>
       </c>
     </row>
@@ -19858,7 +19862,7 @@
           <t>A | 2181呎 (3房)
 $7618万
 $34,928/呎
-(16年-07月-13日)</t>
+(16年-07月-14日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -19874,7 +19878,7 @@
           <t>C | 1412呎 (3房)
 $2980万
 $21,105/呎
-(07年-08月-22日)</t>
+(07年-08月-23日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -19882,7 +19886,7 @@
           <t>D | 1412呎 (3房)
 $6110万
 $43,275/呎
-(15年-09月-10日)</t>
+(15年-09月-11日)</t>
         </is>
       </c>
     </row>
@@ -19897,7 +19901,7 @@
           <t>A | 1070呎 (3房)
 $2900万
 $27,103/呎
-(11年-03月-20日)</t>
+(11年-03月-21日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -19905,7 +19909,7 @@
           <t>B | 1052呎 (3房)
 $3442万
 $32,721/呎
-(16年-01月-06日)</t>
+(16年-01月-07日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -19913,7 +19917,7 @@
           <t>C | 855呎 (3房)
 $2798万
 $32,722/呎
-(15年-12月-27日)</t>
+(15年-12月-28日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -19921,7 +19925,7 @@
           <t>D | 855呎 (3房)
 $2410万
 $28,187/呎
-(11年-05月-18日)</t>
+(11年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -19944,7 +19948,7 @@
           <t>B | 1052呎 (3房)
 $3300万
 $31,369/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -19952,7 +19956,7 @@
           <t>C | 855呎 (3房)
 $2590万
 $30,292/呎
-(26年-03月-31日)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
@@ -19975,7 +19979,7 @@
           <t>A | 1070呎 (3房)
 $1363万
 $12,738/呎
-(02年-01月-01日)</t>
+(02年-01月-02日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -20014,7 +20018,7 @@
           <t>A | 1070呎 (3房)
 $3860万
 $36,075/呎
-(17年-07月-30日)</t>
+(17年-07月-31日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -20022,7 +20026,7 @@
           <t>B | 1052呎 (3房)
 $2789万
 $26,510/呎
-(11年-06月-27日)</t>
+(11年-06月-28日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -20030,7 +20034,7 @@
           <t>C | 855呎 (3房)
 $2511万
 $29,371/呎
-(11年-06月-27日)</t>
+(11年-06月-28日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -20038,7 +20042,7 @@
           <t>D | 855呎 (3房)
 $2850万
 $33,333/呎
-(17年-07月-31日)</t>
+(17年-08月-01日)</t>
         </is>
       </c>
     </row>
@@ -20053,7 +20057,7 @@
           <t>A | 1070呎 (3房)
 $2925万
 $27,336/呎
-(11年-06月-14日)</t>
+(11年-06月-15日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -20061,7 +20065,7 @@
           <t>B | 1052呎 (3房)
 $2663万
 $25,312/呎
-(11年-04月-12日)</t>
+(11年-04月-13日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -20069,7 +20073,7 @@
           <t>C | 855呎 (3房)
 $2700万
 $31,579/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -20077,7 +20081,7 @@
           <t>D | 855呎 (3房)
 $2630万
 $30,760/呎
-(26年-04月-07日)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
     </row>
@@ -20092,7 +20096,7 @@
           <t>A | 1070呎 (3房)
 $2650万
 $24,766/呎
-(10年-12月-30日)</t>
+(10年-12月-31日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -20100,7 +20104,7 @@
           <t>B | 1052呎 (3房)
 $2580万
 $24,525/呎
-(11年-01月-18日)</t>
+(11年-01月-19日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -20108,7 +20112,7 @@
           <t>C | 855呎 (3房)
 $2685万
 $31,399/呎
-(15年-12月-01日)</t>
+(15年-12月-02日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -20116,7 +20120,7 @@
           <t>D | 855呎 (3房)
 $2619万
 $30,628/呎
-(15年-11月-11日)</t>
+(15年-11月-12日)</t>
         </is>
       </c>
     </row>
@@ -20131,7 +20135,7 @@
           <t>A | 1083呎 (3房)
 $1288万
 $11,893/呎
-(02年-01月-01日)</t>
+(02年-01月-02日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -20139,7 +20143,7 @@
           <t>B | 1052呎 (3房)
 $2520万
 $23,954/呎
-(11年-01月-12日)</t>
+(11年-01月-13日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -20147,7 +20151,7 @@
           <t>C | 855呎 (3房)
 $4719万
 $55,189/呎
-(15年-12月-23日)</t>
+(15年-12月-24日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -20155,7 +20159,7 @@
           <t>D | 855呎 (3房)
 $2602万
 $30,436/呎
-(15年-11月-08日)</t>
+(15年-11月-09日)</t>
         </is>
       </c>
     </row>
@@ -20170,7 +20174,7 @@
           <t>A | 1070呎 (3房)
 $2715万
 $25,374/呎
-(11年-01月-23日)</t>
+(11年-01月-24日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -20178,7 +20182,7 @@
           <t>B | 1052呎 (3房)
 $3372万
 $32,055/呎
-(16年-06月-21日)</t>
+(16年-06月-22日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -20186,7 +20190,7 @@
           <t>C | 855呎 (3房)
 $2685万
 $31,399/呎
-(15年-09月-29日)</t>
+(15年-09月-30日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -20194,7 +20198,7 @@
           <t>D | 855呎 (3房)
 $2265万
 $26,491/呎
-(11年-01月-23日)</t>
+(11年-01月-24日)</t>
         </is>
       </c>
     </row>
@@ -20233,7 +20237,7 @@
           <t>D | 855呎 (3房)
 $988万
 $11,557/呎
-(02年-01月-08日)</t>
+(02年-01月-09日)</t>
         </is>
       </c>
     </row>
@@ -20248,7 +20252,7 @@
           <t>A | 1052呎 (3房)
 $3376万
 $32,095/呎
-(16年-06月-13日)</t>
+(16年-06月-14日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -20256,7 +20260,7 @@
           <t>B | 1032呎 (3房)
 $2448万
 $23,721/呎
-(11年-05月-29日)</t>
+(11年-05月-30日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -20264,7 +20268,7 @@
           <t>C | 841呎 (3房)
 $1792万
 $21,307/呎
-(08年-03月-26日)</t>
+(08年-03月-27日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -20272,7 +20276,7 @@
           <t>D | 841呎 (3房)
 $2560万
 $30,440/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
     </row>
@@ -20287,7 +20291,7 @@
           <t>A | 1052呎 (3房)
 $1192万
 $11,335/呎
-(02年-01月-01日)</t>
+(02年-01月-02日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -20295,7 +20299,7 @@
           <t>B | 1032呎 (3房)
 $2250万
 $21,802/呎
-(11年-01月-16日)</t>
+(11年-01月-17日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -20303,7 +20307,7 @@
           <t>C | 841呎 (3房)
 $2080万
 $24,732/呎
-(11年-01月-26日)</t>
+(11年-01月-27日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -20311,7 +20315,7 @@
           <t>D | 841呎 (3房)
 $2154万
 $25,612/呎
-(11年-06月-01日)</t>
+(11年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -20326,7 +20330,7 @@
           <t>A | 1065呎 (3房)
 $2350万
 $22,066/呎
-(11年-01月-23日)</t>
+(11年-01月-24日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -20334,7 +20338,7 @@
           <t>B | 1032呎 (3房)
 $2210万
 $21,415/呎
-(11年-01月-16日)</t>
+(11年-01月-17日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -20350,7 +20354,7 @@
           <t>D | 865呎 (3房)
 $920万
 $10,631/呎
-(02年-04月-19日)</t>
+(02年-04月-20日)</t>
         </is>
       </c>
     </row>
@@ -20365,7 +20369,7 @@
           <t>A | 1052呎 (3房)
 $1167万
 $11,093/呎
-(02年-01月-08日)</t>
+(02年-01月-09日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -20373,7 +20377,7 @@
           <t>B | 1032呎 (3房)
 $2160万
 $20,930/呎
-(11年-01月-18日)</t>
+(11年-01月-19日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -20381,7 +20385,7 @@
           <t>C | 841呎 (3房)
 $2083万
 $24,768/呎
-(11年-03月-08日)</t>
+(11年-03月-09日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -20389,7 +20393,7 @@
           <t>D | 841呎 (3房)
 $2118万
 $25,184/呎
-(11年-06月-13日)</t>
+(11年-06月-14日)</t>
         </is>
       </c>
     </row>
@@ -20404,7 +20408,7 @@
           <t>A | 1052呎 (3房)
 $1210万
 $11,507/呎
-(02年-01月-16日)</t>
+(02年-01月-17日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -20412,7 +20416,7 @@
           <t>B | 1038呎 (3房)
 $2160万
 $20,809/呎
-(11年-01月-06日)</t>
+(11年-01月-07日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -20420,7 +20424,7 @@
           <t>C | 840呎 (2房)
 $1960万
 $23,333/呎
-(11年-01月-18日)</t>
+(11年-01月-19日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -20428,7 +20432,7 @@
           <t>D | 841呎 (3房)
 $2380万
 $28,299/呎
-(15年-11月-05日)</t>
+(15年-11月-06日)</t>
         </is>
       </c>
     </row>
@@ -20443,15 +20447,15 @@
           <t>A | 1052呎 (3房)
 $1197万
 $11,378/呎
-(02年-01月-01日)</t>
-        </is>
-      </c>
-      <c r="C21" s="21" t="inlineStr">
+(02年-01月-02日)</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>B | 1032呎 (3房)
+招标单位
 -
--
-(待售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -20459,7 +20463,7 @@
           <t>C | 840呎 (2房)
 $1990万
 $23,690/呎
-(11年-01月-23日)</t>
+(11年-01月-24日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -20467,7 +20471,7 @@
           <t>D | 841呎 (3房)
 $2000万
 $23,781/呎
-(11年-03月-16日)</t>
+(11年-03月-17日)</t>
         </is>
       </c>
     </row>
@@ -20482,7 +20486,7 @@
           <t>A | 1064呎 (3房)
 $1125万
 $10,573/呎
-(02年-01月-01日)</t>
+(02年-01月-02日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -20490,7 +20494,7 @@
           <t>B | 1032呎 (3房)
 $2100万
 $20,349/呎
-(11年-01月-17日)</t>
+(11年-01月-18日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -20498,7 +20502,7 @@
           <t>C | 840呎 (2房)
 $1900万
 $22,619/呎
-(11年-01月-13日)</t>
+(11年-01月-14日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -20506,7 +20510,7 @@
           <t>D | 841呎 (3房)
 $946万
 $11,253/呎
-(02年-01月-01日)</t>
+(02年-01月-02日)</t>
         </is>
       </c>
     </row>
@@ -20521,7 +20525,7 @@
           <t>A | 1052呎 (3房)
 $1140万
 $10,833/呎
-(02年-01月-08日)</t>
+(02年-01月-09日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -20529,7 +20533,7 @@
           <t>B | 1038呎 (3房)
 $2140万
 $20,617/呎
-(11年-01月-16日)</t>
+(11年-01月-17日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -20537,7 +20541,7 @@
           <t>C | 840呎 (2房)
 $1990万
 $23,690/呎
-(11年-01月-30日)</t>
+(11年-01月-31日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -20545,7 +20549,7 @@
           <t>D | 841呎 (3房)
 $2363万
 $28,103/呎
-(15年-11月-12日)</t>
+(15年-11月-13日)</t>
         </is>
       </c>
     </row>
@@ -20560,7 +20564,7 @@
           <t>A | 1052呎 (3房)
 $1015万
 $9,651/呎
-(02年-01月-01日)</t>
+(02年-01月-02日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -20568,7 +20572,7 @@
           <t>B | 1032呎 (3房)
 $953万
 $9,232/呎
-(02年-01月-01日)</t>
+(02年-01月-02日)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -20584,7 +20588,7 @@
           <t>D | 841呎 (3房)
 $946万
 $11,249/呎
-(02年-01月-09日)</t>
+(02年-01月-10日)</t>
         </is>
       </c>
     </row>
@@ -20599,7 +20603,7 @@
           <t>A | 1052呎 (3房)
 $1064万
 $10,113/呎
-(02年-01月-01日)</t>
+(02年-01月-02日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -20607,7 +20611,7 @@
           <t>B | 1032呎 (3房)
 $1950万
 $18,895/呎
-(10年-12月-30日)</t>
+(10年-12月-31日)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -20623,7 +20627,7 @@
           <t>D | 841呎 (3房)
 $896万
 $10,649/呎
-(02年-01月-01日)</t>
+(02年-01月-02日)</t>
         </is>
       </c>
     </row>
@@ -20638,7 +20642,7 @@
           <t>A | 1064呎 (3房)
 $1061万
 $9,976/呎
-(01年-12月-28日)</t>
+(01年-12月-29日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -20646,7 +20650,7 @@
           <t>B | 1032呎 (3房)
 $1938万
 $18,779/呎
-(11年-01月-13日)</t>
+(11年-01月-14日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -20654,7 +20658,7 @@
           <t>C | 863呎 (2房)
 $1810万
 $20,973/呎
-(11年-01月-10日)</t>
+(11年-01月-11日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -20662,7 +20666,7 @@
           <t>D | 841呎 (3房)
 $1838万
 $21,855/呎
-(11年-01月-31日)</t>
+(11年-02月-01日)</t>
         </is>
       </c>
     </row>
@@ -20677,7 +20681,7 @@
           <t>A | 1064呎 (3房)
 $1040万
 $9,773/呎
-(02年-01月-08日)</t>
+(02年-01月-09日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -20685,7 +20689,7 @@
           <t>B | 1032呎 (3房)
 $1900万
 $18,411/呎
-(10年-12月-28日)</t>
+(10年-12月-29日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -20693,7 +20697,7 @@
           <t>C | 840呎 (2房)
 $1740万
 $20,714/呎
-(11年-01月-11日)</t>
+(11年-01月-12日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -20701,7 +20705,7 @@
           <t>D | 841呎 (3房)
 $1790万
 $21,284/呎
-(11年-01月-23日)</t>
+(11年-01月-24日)</t>
         </is>
       </c>
     </row>
@@ -20716,7 +20720,7 @@
           <t>A | 1065呎 (3房)
 $942万
 $8,848/呎
-(02年-01月-01日)</t>
+(02年-01月-02日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -20724,7 +20728,7 @@
           <t>B | 1032呎 (3房)
 $1867万
 $18,094/呎
-(10年-12月-19日)</t>
+(10年-12月-20日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -20732,7 +20736,7 @@
           <t>C | 865呎 (2房)
 $1723万
 $19,916/呎
-(10年-12月-19日)</t>
+(10年-12月-20日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -20740,7 +20744,7 @@
           <t>D | 841呎 (3房)
 $913万
 $10,856/呎
-(02年-01月-01日)</t>
+(02年-01月-02日)</t>
         </is>
       </c>
     </row>
@@ -20755,7 +20759,7 @@
           <t>A | 1042呎 (3房)
 $1065万
 $10,221/呎
-(02年-01月-01日)</t>
+(02年-01月-02日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -20763,7 +20767,7 @@
           <t>B | 1032呎 (3房)
 $1918万
 $18,585/呎
-(11年-01月-05日)</t>
+(11年-01月-06日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -20771,7 +20775,7 @@
           <t>C | 840呎 (2房)
 $881万
 $10,492/呎
-(02年-01月-01日)</t>
+(02年-01月-02日)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
@@ -20779,7 +20783,7 @@
           <t>D | 841呎 (3房)
 $733万
 $8,721/呎
-(02年-01月-07日)</t>
+(02年-01月-08日)</t>
         </is>
       </c>
     </row>
@@ -20794,7 +20798,7 @@
           <t>A | 1042呎 (3房)
 $1015万
 $9,740/呎
-(02年-03月-15日)</t>
+(02年-03月-16日)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -20802,7 +20806,7 @@
           <t>B | 1039呎 (3房)
 $892万
 $8,586/呎
-(02年-01月-09日)</t>
+(02年-01月-10日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -20810,7 +20814,7 @@
           <t>C | 840呎 (2房)
 $1780万
 $21,190/呎
-(11年-01月-20日)</t>
+(11年-01月-21日)</t>
         </is>
       </c>
       <c r="E30" s="21" t="inlineStr">
@@ -20833,7 +20837,7 @@
           <t>A | 1056呎 (3房)
 $832万
 $7,877/呎
-(02年-01月-08日)</t>
+(02年-01月-09日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -20841,7 +20845,7 @@
           <t>B | 1032呎 (3房)
 $840万
 $8,140/呎
-(01年-12月-28日)</t>
+(01年-12月-29日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -20849,7 +20853,7 @@
           <t>C | 840呎 (2房)
 $750万
 $8,935/呎
-(02年-01月-08日)</t>
+(02年-01月-09日)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -20857,7 +20861,7 @@
           <t>D | 865呎 (3房)
 $769万
 $8,890/呎
-(02年-01月-08日)</t>
+(02年-01月-09日)</t>
         </is>
       </c>
     </row>
@@ -20872,7 +20876,7 @@
           <t>A | 1042呎 (3房)
 $858万
 $8,234/呎
-(02年-01月-01日)</t>
+(02年-01月-02日)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -20880,7 +20884,7 @@
           <t>B | 618呎 (2房)
 $487万
 $7,880/呎
-(02年-01月-01日)</t>
+(02年-01月-02日)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -20888,7 +20892,7 @@
           <t>C | 840呎 (2房)
 $791万
 $9,417/呎
-(02年-01月-01日)</t>
+(02年-01月-02日)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -20896,7 +20900,7 @@
           <t>D | 841呎 (2房)
 $733万
 $8,717/呎
-(02年-01月-09日)</t>
+(02年-01月-10日)</t>
         </is>
       </c>
     </row>
@@ -20911,7 +20915,7 @@
           <t>A | 1042呎 (3房)
 $891万
 $8,548/呎
-(02年-01月-01日)</t>
+(02年-01月-02日)</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
@@ -20919,7 +20923,7 @@
           <t>B | 619呎 (2房)
 $486万
 $7,851/呎
-(02年-01月-01日)</t>
+(02年-01月-02日)</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -20927,7 +20931,7 @@
           <t>C | 840呎 (2房)
 $723万
 $8,607/呎
-(02年-01月-07日)</t>
+(02年-01月-08日)</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
@@ -20935,7 +20939,7 @@
           <t>D | 841呎 (2房)
 $715万
 $8,501/呎
-(02年-01月-01日)</t>
+(02年-01月-02日)</t>
         </is>
       </c>
     </row>
@@ -20950,7 +20954,7 @@
           <t>A | 1042呎 (3房)
 $828万
 $7,947/呎
-(01年-12月-27日)</t>
+(01年-12月-28日)</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
@@ -20958,7 +20962,7 @@
           <t>B | 618呎 (2房)
 $481万
 $7,783/呎
-(01年-12月-27日)</t>
+(01年-12月-28日)</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
@@ -20966,7 +20970,7 @@
           <t>C | 840呎 (2房)
 $709万
 $8,445/呎
-(01年-12月-27日)</t>
+(01年-12月-28日)</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr">
@@ -20974,7 +20978,7 @@
           <t>D | 865呎 (2房)
 $754万
 $8,716/呎
-(02年-01月-09日)</t>
+(02年-01月-10日)</t>
         </is>
       </c>
     </row>
@@ -20989,7 +20993,7 @@
           <t>A | 1042呎 (3房)
 $866万
 $8,311/呎
-(02年-01月-08日)</t>
+(02年-01月-09日)</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
@@ -20997,7 +21001,7 @@
           <t>B | 618呎 (2房)
 $426万
 $6,893/呎
-(02年-01月-08日)</t>
+(02年-01月-09日)</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
@@ -21005,7 +21009,7 @@
           <t>C | 840呎 (2房)
 $650万
 $7,736/呎
-(02年-01月-08日)</t>
+(02年-01月-09日)</t>
         </is>
       </c>
       <c r="E35" s="20" t="inlineStr">
@@ -21013,7 +21017,7 @@
           <t>D | 840呎 (2房)
 $1490万
 $17,738/呎
-(11年-01月-16日)</t>
+(11年-01月-17日)</t>
         </is>
       </c>
     </row>
@@ -21028,7 +21032,7 @@
           <t>A | 1056呎 (3房)
 $855万
 $8,097/呎
-(02年-01月-01日)</t>
+(02年-01月-02日)</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
@@ -21036,7 +21040,7 @@
           <t>B | 618呎 (2房)
 $456万
 $7,385/呎
-(02年-01月-01日)</t>
+(02年-01月-02日)</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
@@ -21044,7 +21048,7 @@
           <t>C | 840呎 (2房)
 $724万
 $8,625/呎
-(02年-01月-01日)</t>
+(02年-01月-02日)</t>
         </is>
       </c>
       <c r="E36" s="20" t="inlineStr">
@@ -21052,7 +21056,7 @@
           <t>D | 840呎 (2房)
 $718万
 $8,548/呎
-(02年-01月-01日)</t>
+(02年-01月-02日)</t>
         </is>
       </c>
     </row>
@@ -21067,7 +21071,7 @@
           <t>A | 1042呎 (3房)
 $760万
 $7,295/呎
-(02年-01月-09日)</t>
+(02年-01月-10日)</t>
         </is>
       </c>
       <c r="C37" s="20" t="inlineStr">
@@ -21075,7 +21079,7 @@
           <t>B | 618呎 (2房)
 $373万
 $6,042/呎
-(01年-12月-30日)</t>
+(01年-12月-31日)</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
@@ -21083,7 +21087,7 @@
           <t>C | 840呎 (2房)
 $707万
 $8,417/呎
-(01年-12月-28日)</t>
+(01年-12月-29日)</t>
         </is>
       </c>
       <c r="E37" s="20" t="inlineStr">
@@ -21091,7 +21095,7 @@
           <t>D | 840呎 (2房)
 $667万
 $7,936/呎
-(01年-12月-28日)</t>
+(01年-12月-29日)</t>
         </is>
       </c>
     </row>
@@ -21106,7 +21110,7 @@
           <t>A | 1042呎 (3房)
 $732万
 $7,022/呎
-(01年-12月-28日)</t>
+(01年-12月-29日)</t>
         </is>
       </c>
       <c r="C38" s="22" t="inlineStr"/>
@@ -21116,7 +21120,7 @@
           <t>D | 840呎 (2房)
 $662万
 $7,875/呎
-(02年-01月-09日)</t>
+(02年-01月-10日)</t>
         </is>
       </c>
     </row>

--- a/港岛-半山区西部-罗便臣道80号/罗便臣道80号_销控明细表.xlsx
+++ b/港岛-半山区西部-罗便臣道80号/罗便臣道80号_销控明细表.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -125,11 +125,6 @@
       <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="8"/>
-    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -207,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -273,9 +268,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -13815,23 +13807,19 @@
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H199" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I199" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H199" s="5" t="n">
+        <v>30280000</v>
+      </c>
+      <c r="I199" s="5" t="n">
+        <v>29341</v>
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
@@ -13840,12 +13828,12 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L199" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M199" s="3" t="inlineStr">
@@ -13855,7 +13843,7 @@
       </c>
       <c r="N199" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -19766,12 +19754,12 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>120</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -20450,12 +20438,12 @@
 (02年-01月-02日)</t>
         </is>
       </c>
-      <c r="C21" s="23" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 1032呎 (3房)
-招标单位
--
-(已定价未售)</t>
+$3028万
+$29,341/呎
+(26年-08月-04日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">

--- a/港岛-半山区西部-罗便臣道80号/罗便臣道80号_销控明细表.xlsx
+++ b/港岛-半山区西部-罗便臣道80号/罗便臣道80号_销控明细表.xlsx
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1083</v>
+        <v>1070</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
         <v>36800000</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>33980</v>
+        <v>34393</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -18537,10 +18537,10 @@
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>B | 1083呎 (3房)
+          <t>B | 1070呎 (3房)
 $3680万
-$33,980/呎
-(26年-07月-24日)</t>
+$34,393/呎
+(26年-08月-17日)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">

--- a/港岛-半山区西部-罗便臣道80号/罗便臣道80号_销控明细表.xlsx
+++ b/港岛-半山区西部-罗便臣道80号/罗便臣道80号_销控明细表.xlsx
@@ -13812,7 +13812,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -20443,7 +20443,7 @@
           <t>B | 1032呎 (3房)
 $3028万
 $29,341/呎
-(26年-08月-04日)</t>
+(26年-08月-31日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">

--- a/港岛-半山区西部-罗便臣道80号/罗便臣道80号_销控明细表.xlsx
+++ b/港岛-半山区西部-罗便臣道80号/罗便臣道80号_销控明细表.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -125,6 +125,12 @@
       <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -202,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -268,6 +274,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -10409,7 +10418,7 @@
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
@@ -10419,12 +10428,12 @@
       </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I148" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J148" s="3" t="inlineStr">
@@ -10434,12 +10443,12 @@
       </c>
       <c r="K148" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L148" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M148" s="3" t="inlineStr">
@@ -10449,7 +10458,7 @@
       </c>
       <c r="N148" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -19749,27 +19758,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -19923,12 +19932,12 @@
           <t>46</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>A | 1070呎 (3房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
